--- a/samples/monthly_report/월간실적_생산팀.xlsx
+++ b/samples/monthly_report/월간실적_생산팀.xlsx
@@ -450,27 +450,27 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>기준월</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>KPI</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
           <t>팀명</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>기준월</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>KPI</t>
-        </is>
-      </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
+          <t>Actual</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
           <t>Target</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Actual</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -482,24 +482,24 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>생산팀</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>생산량(EA)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>생산량(EA)</t>
+          <t>생산팀</t>
         </is>
       </c>
       <c r="D4" t="n">
+        <v>52876.5</v>
+      </c>
+      <c r="E4" t="n">
         <v>52000</v>
-      </c>
-      <c r="E4" t="n">
-        <v>52876.5</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -510,88 +510,88 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>생산팀</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-08</t>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>생산팀</t>
         </is>
       </c>
       <c r="D5" t="n">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="E5" t="n">
         <v>85</v>
-      </c>
-      <c r="E5" t="n">
-        <v>79.09999999999999</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>생산팀</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>설비고장시간(h)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>설비고장시간(h)</t>
+          <t>생산팀</t>
         </is>
       </c>
       <c r="D6" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="E6" t="n">
         <v>20</v>
-      </c>
-      <c r="E6" t="n">
-        <v>19.7</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>생산팀</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>인시당생산성(EA)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>인시당생산성(EA)</t>
+          <t>생산팀</t>
         </is>
       </c>
       <c r="D7" t="n">
+        <v>37</v>
+      </c>
+      <c r="E7" t="n">
         <v>35</v>
-      </c>
-      <c r="E7" t="n">
-        <v>37</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>생산팀</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>납기준수율(%)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>납기준수율(%)</t>
+          <t>생산팀</t>
         </is>
       </c>
       <c r="D8" t="n">
+        <v>-120</v>
+      </c>
+      <c r="E8" t="n">
         <v>98</v>
-      </c>
-      <c r="E8" t="n">
-        <v>-120</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -602,24 +602,24 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>생산팀</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>재공재고(EA)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>재공재고(EA)</t>
+          <t>생산팀</t>
         </is>
       </c>
       <c r="D9" t="n">
+        <v>4037.3</v>
+      </c>
+      <c r="E9" t="n">
         <v>4000</v>
-      </c>
-      <c r="E9" t="n">
-        <v>4037.3</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -630,111 +630,111 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>생산팀</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>잔업시간(h)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>잔업시간(h)</t>
+          <t>생산팀</t>
         </is>
       </c>
       <c r="D10" t="n">
+        <v>294.8</v>
+      </c>
+      <c r="E10" t="n">
         <v>300</v>
-      </c>
-      <c r="E10" t="n">
-        <v>294.8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>생산팀</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>공정불량률(ppm)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>공정불량률(ppm)</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
+          <t>생산팀</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>453</v>
+      </c>
+      <c r="E11" t="inlineStr">
         <is>
           <t>약 500</t>
         </is>
-      </c>
-      <c r="E11" t="n">
-        <v>453</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>생산팀</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>에너지사용량(MWh)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>에너지사용량(MWh)</t>
+          <t>생산팀</t>
         </is>
       </c>
       <c r="D12" t="n">
+        <v>179.8</v>
+      </c>
+      <c r="E12" t="n">
         <v>180</v>
-      </c>
-      <c r="E12" t="n">
-        <v>179.8</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>생산팀</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>원가절감(백만원)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>원가절감(백만원)</t>
+          <t>생산팀</t>
         </is>
       </c>
       <c r="D13" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="E13" t="n">
         <v>30</v>
-      </c>
-      <c r="E13" t="n">
-        <v>26.5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>생산팀</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>안전사고건수</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>안전사고건수</t>
+          <t>생산팀</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -752,24 +752,24 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>생산팀</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>작업자수</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>작업자수</t>
+          <t>생산팀</t>
         </is>
       </c>
       <c r="D15" t="n">
+        <v>58.5</v>
+      </c>
+      <c r="E15" t="n">
         <v>64</v>
-      </c>
-      <c r="E15" t="n">
-        <v>58.5</v>
       </c>
     </row>
   </sheetData>
